--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/LOUISIANA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/LOUISIANA_2014.xlsx
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C170">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C179">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C408">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C756">
